--- a/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
+++ b/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
@@ -372,7 +372,7 @@
     <t>Harshita</t>
   </si>
   <si>
-    <t>Next.js, Nuxt or Vite. Developer's choice; justify it in README | 23 Oct (Harshita): Next.js (App Router, JavaScript), GSAP + ScrollTrigger, Phosphor Regular, three.js, fonts self-hosted via next/font. Lenis not used: it broke programmatic and anchor scrolling in testing (DESIGN.md §7 allows it only if native scroll is unaffected). Initial JS about 175KB gzip vs 100KB target (Next.js + React runtime is about 160KB).</t>
+    <t>Next.js, Nuxt or Vite. Developer's choice; justify it in README | 23 Oct (Harshita): Next.js (App Router, JavaScript), GSAP + ScrollTrigger, Phosphor Regular, three.js, fonts self-hosted via next/font. Lenis not used: it broke programmatic and anchor scrolling in testing (DESIGN.md §7 allows it only if native scroll is unaffected). Initial JS about 175KB gzip vs 100KB target (Next.js + React runtime is about 160KB). | 24 Oct (Harshita): Header now lists the 8 Must pages in build order: Home, How it works, Builders, Compare (menu: hub, Bottled water, RO filters), Environment, and Contact as the header button; the phone menu and footer list all 8. Compare hub, both comparisons, Environment and Contact show marked holding pages (PLACEHOLDER, not indexed) until each is built in order. All 8 routes return 200. Audit: Impeccable detect 0 findings; Taste lint 0 FAIL.</t>
   </si>
   <si>
     <t>E2</t>

--- a/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
+++ b/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
@@ -381,7 +381,7 @@
     <t>Build home page (consumer first, builders teaser)</t>
   </si>
   <si>
-    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button).</t>
+    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens.</t>
   </si>
   <si>
     <t>E3</t>
@@ -411,7 +411,7 @@
     <t>Build interactions: recharge demo, app panel, how it works</t>
   </si>
   <si>
-    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light).</t>
+    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens.</t>
   </si>
   <si>
     <t>E7</t>

--- a/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
+++ b/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
@@ -381,7 +381,7 @@
     <t>Build home page (consumer first, builders teaser)</t>
   </si>
   <si>
-    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens.</t>
+    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
   </si>
   <si>
     <t>E3</t>
@@ -411,7 +411,7 @@
     <t>Build interactions: recharge demo, app panel, how it works</t>
   </si>
   <si>
-    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens.</t>
+    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
   </si>
   <si>
     <t>E7</t>

--- a/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
+++ b/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
@@ -381,7 +381,7 @@
     <t>Build home page (consumer first, builders teaser)</t>
   </si>
   <si>
-    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
+    <t>23 Oct (Harshita): Home built and approved hero in place; Moya1™ added; unconfirmed product lines marked PLACEHOLDER (see Claims). Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter flagged as a default face, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D and bans stock imagery) and covered-text (sticky 3D stage on phones; floating WhatsApp button). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size. | 24 Oct (Harshita): Per feedback, the start-to-end story is now a full-bleed, full-screen opening like the film (words on the left as captions, drawing filling the screen, 1-6 row): the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
   </si>
   <si>
     <t>E3</t>
@@ -411,7 +411,7 @@
     <t>Build interactions: recharge demo, app panel, how it works</t>
   </si>
   <si>
-    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
+    <t>Keep numbers labelled 'sample' | 23 Oct (Harshita): Home: sample recharge demo, 3D kitchen film, tower climb with floor counter (Illustrative). How it works: scroll-driven 3D journey (tower, then kitchen). | 23 Oct (Harshita): Builders: tower construct mode (floors build in order, line follows, kitchens light). | 24 Oct (Harshita): How it works now opens with a start-to-end story: one drawing that plays six steps in order (builder plans it in, line laid to every flat, kitchen fitted, then you recharge, pour, top up), with the steps listed beside it; Pause/Play, tap any step; phones show the picture, the current step and a 1-6 row. Film and Try it follow. All drawings labelled Illustrative; no numbers, no prices, no tech detail; no filter claim kept as PLACEHOLDER. Checked 390px and 1440px (no horizontal scroll), reduced motion (starts paused, finished pictures). Audit: Impeccable detect 0 findings; Taste lint 0 FAIL; inspector FAILs are the documented exceptions (few-pictures: SVG/3D only per CLAUDE.md; drop title sits on a solid ink panel over the film). Fixed: class clash with the home hero, mobile layout, font sizes to tokens. | 24 Oct (Harshita): Per feedback, the start-to-end story is now the full-screen opening: the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size. | 24 Oct (Harshita): Per feedback, the start-to-end story is now a full-bleed, full-screen opening like the film (words on the left as captions, drawing filling the screen, 1-6 row): the view is pinned and scrolling moves through the six steps one by one (picture changes, step highlights, progress bar fills); tapping a step scrolls to it. Checked 390px and 1440px, no horizontal scroll, all six steps reached by scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = documented few-pictures exception (SVG/3D only per CLAUDE.md). Fixed: mobile h1 size.</t>
   </si>
   <si>
     <t>E7</t>

--- a/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
+++ b/Moya_One_Harshita_Handover/Moya_One_Project_Tracker.xlsx
@@ -390,7 +390,7 @@
     <t>Build builders page (with embedded MP4 video)</t>
   </si>
   <si>
-    <t>Video is an MP4 file, not a coded animation | 23 Oct (Harshita): Builders page built (/b2b/builders): dark hero with a 3D tower that builds itself floor by floor as the line rises (new construct mode), ledger of what it asks of a project beside the 3D kitchen close-up, explainer film slot, reference projects, enquiry close. Not done: the brief requires the MP4 to play on mobile and the approved cut does not exist yet (F3, F4); the slot lazy-loads it once BUILDER_VIDEO.src is set in lib/content.js. Reference projects are placeholders marked "To confirm" (no names). "No retrofit", "No lost space" and "its own plant room" marked PLACEHOLDER (Claims: To confirm). Enquiry goes to the placeholder email until /contact exists. Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D, no stock imagery) and covered-text (floating WhatsApp button at 390px). 390px and 1440px: no horizontal scroll. Reduced motion: final state, no hidden text.</t>
+    <t>Video is an MP4 file, not a coded animation | 23 Oct (Harshita): Builders page built (/b2b/builders): dark hero with a 3D tower that builds itself floor by floor as the line rises (new construct mode), ledger of what it asks of a project beside the 3D kitchen close-up, explainer film slot, reference projects, enquiry close. Not done: the brief requires the MP4 to play on mobile and the approved cut does not exist yet (F3, F4); the slot lazy-loads it once BUILDER_VIDEO.src is set in lib/content.js. Reference projects are placeholders marked "To confirm" (no names). "No retrofit", "No lost space" and "its own plant room" marked PLACEHOLDER (Claims: To confirm). Enquiry goes to the placeholder email until /contact exists. Audit: not a full pass yet. Impeccable detect 0 findings; Taste lint 0 FAIL (1 WARN: Inter, pinned by DESIGN.md). Taste inspect leaves 2 FAILs as documented exceptions for Vinayak: few-pictures (CLAUDE.md requires SVG/3D, no stock imagery) and covered-text (floating WhatsApp button at 390px). 390px and 1440px: no horizontal scroll. Reduced motion: final state, no hidden text. | 24 Oct (Harshita): Builders page rebuilt from scratch per feedback (premium, easy, unlike other pages): dark hero with a real construction photo; the construction schedule (Design, Structure, Services, Finishing, Handover) with Moya One at each stage; a dusk crane band; what goes into a flat and what stays out, beside a kitchen photo; a live sizer (floors x flats per floor redraws a tower section with one line to every flat, counts labelled Illustrative, no prices); an enquiry form that fills an email with the sized tower (placeholder address). Removed: 3D construct tower, film slot and placeholder references (return once the film and approved projects exist). Photos: Unsplash License (James Sullivan, EJ Yao, Filip Baotic, Zoshua Colah), credited on the page, PLACEHOLDER until client approves. Stage mapping and plant room/no filter/no retrofit lines marked PLACEHOLDER. Checked 390 and 1440, no horizontal scroll. Audit: Impeccable detect 0; Taste lint 0 FAIL; inspector 1 FAIL = shared footer wordmark under the sticky nav. Fixed: headline lengths, covered heading on phones, WhatsApp button now hides as soon as the footer enters.</t>
   </si>
   <si>
     <t>E4</t>
